--- a/all_years.xlsx
+++ b/all_years.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30131"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30430"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\own_prog\github\kaudet\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F86F6680-2F9F-45D3-9DE1-64CA7380FA8C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E9EF01E6-112C-4940-B11E-62B3657A1D17}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="1968" yWindow="1452" windowWidth="21072" windowHeight="12948" tabRatio="880" xr2:uid="{CFC6D258-5D3C-46F8-BFEC-F3C271445404}"/>
+    <workbookView xWindow="4500" yWindow="1416" windowWidth="17280" windowHeight="11580" tabRatio="880" xr2:uid="{CFC6D258-5D3C-46F8-BFEC-F3C271445404}"/>
   </bookViews>
   <sheets>
     <sheet name="all" sheetId="10" r:id="rId1"/>
@@ -490,41 +490,45 @@
       <xxl21:absoluteUrl r:id="rId2"/>
     </xxl21:alternateUrls>
     <sheetNames>
-      <sheetName val="A 2025-2027"/>
-      <sheetName val="A 2026-2027"/>
-      <sheetName val="A 2025-2026"/>
+      <sheetName val="B 2023-2027"/>
+      <sheetName val="B 2026-2027"/>
+      <sheetName val="B 2025-2026"/>
+      <sheetName val="B 2024-2025"/>
+      <sheetName val="B 2023-2024"/>
     </sheetNames>
     <sheetDataSet>
       <sheetData sheetId="0">
-        <row r="4">
-          <cell r="C4">
-            <v>19</v>
-          </cell>
-          <cell r="D4">
-            <v>10</v>
-          </cell>
-          <cell r="E4">
-            <v>0</v>
-          </cell>
-          <cell r="F4">
-            <v>9</v>
-          </cell>
-          <cell r="G4">
-            <v>23</v>
-          </cell>
-          <cell r="H4">
-            <v>19</v>
-          </cell>
-          <cell r="I4">
-            <v>973</v>
-          </cell>
-          <cell r="J4">
-            <v>943</v>
+        <row r="6">
+          <cell r="C6">
+            <v>73</v>
+          </cell>
+          <cell r="D6">
+            <v>34</v>
+          </cell>
+          <cell r="E6">
+            <v>7</v>
+          </cell>
+          <cell r="F6">
+            <v>32</v>
+          </cell>
+          <cell r="G6">
+            <v>75</v>
+          </cell>
+          <cell r="H6">
+            <v>72</v>
+          </cell>
+          <cell r="I6">
+            <v>3461</v>
+          </cell>
+          <cell r="J6">
+            <v>3480</v>
           </cell>
         </row>
       </sheetData>
       <sheetData sheetId="1"/>
       <sheetData sheetId="2"/>
+      <sheetData sheetId="3"/>
+      <sheetData sheetId="4"/>
     </sheetDataSet>
   </externalBook>
 </externalLink>
@@ -537,7 +541,55 @@
       <xxl21:absoluteUrl r:id="rId2"/>
     </xxl21:alternateUrls>
     <sheetNames>
+      <sheetName val="A 2025-2027"/>
+      <sheetName val="A 2026-2027"/>
+      <sheetName val="A 2025-2026"/>
+    </sheetNames>
+    <sheetDataSet>
+      <sheetData sheetId="0">
+        <row r="4">
+          <cell r="C4">
+            <v>19</v>
+          </cell>
+          <cell r="D4">
+            <v>10</v>
+          </cell>
+          <cell r="E4">
+            <v>0</v>
+          </cell>
+          <cell r="F4">
+            <v>9</v>
+          </cell>
+          <cell r="G4">
+            <v>23</v>
+          </cell>
+          <cell r="H4">
+            <v>19</v>
+          </cell>
+          <cell r="I4">
+            <v>973</v>
+          </cell>
+          <cell r="J4">
+            <v>943</v>
+          </cell>
+        </row>
+      </sheetData>
+      <sheetData sheetId="1"/>
+      <sheetData sheetId="2"/>
+    </sheetDataSet>
+  </externalBook>
+</externalLink>
+</file>
+
+<file path=xl/externalLinks/externalLink6.xml><?xml version="1.0" encoding="utf-8"?>
+<externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xxl21="http://schemas.microsoft.com/office/spreadsheetml/2021/extlinks2021" mc:Ignorable="x14 xxl21">
+  <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
+    <xxl21:alternateUrls>
+      <xxl21:absoluteUrl r:id="rId2"/>
+    </xxl21:alternateUrls>
+    <sheetNames>
       <sheetName val="M2 2025-2027"/>
+      <sheetName val="M2 2026-2027"/>
       <sheetName val="M2 2025-2026"/>
     </sheetNames>
     <sheetDataSet>
@@ -568,12 +620,13 @@
         </row>
       </sheetData>
       <sheetData sheetId="1"/>
+      <sheetData sheetId="2"/>
     </sheetDataSet>
   </externalBook>
 </externalLink>
 </file>
 
-<file path=xl/externalLinks/externalLink6.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/externalLinks/externalLink7.xml><?xml version="1.0" encoding="utf-8"?>
 <externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xxl21="http://schemas.microsoft.com/office/spreadsheetml/2021/extlinks2021" mc:Ignorable="x14 xxl21">
   <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
     <xxl21:alternateUrls>
@@ -630,7 +683,7 @@
 </externalLink>
 </file>
 
-<file path=xl/externalLinks/externalLink7.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/externalLinks/externalLink8.xml><?xml version="1.0" encoding="utf-8"?>
 <externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xxl21="http://schemas.microsoft.com/office/spreadsheetml/2021/extlinks2021" mc:Ignorable="x14 xxl21">
   <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
     <xxl21:alternateUrls>
@@ -682,57 +735,6 @@
       <sheetData sheetId="5"/>
       <sheetData sheetId="6"/>
       <sheetData sheetId="7"/>
-    </sheetDataSet>
-  </externalBook>
-</externalLink>
-</file>
-
-<file path=xl/externalLinks/externalLink8.xml><?xml version="1.0" encoding="utf-8"?>
-<externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xxl21="http://schemas.microsoft.com/office/spreadsheetml/2021/extlinks2021" mc:Ignorable="x14 xxl21">
-  <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
-    <xxl21:alternateUrls>
-      <xxl21:absoluteUrl r:id="rId2"/>
-    </xxl21:alternateUrls>
-    <sheetNames>
-      <sheetName val="B 2023-2027"/>
-      <sheetName val="B 2026-2027"/>
-      <sheetName val="B 2025-2026"/>
-      <sheetName val="B 2024-2025"/>
-      <sheetName val="B 2023-2024"/>
-    </sheetNames>
-    <sheetDataSet>
-      <sheetData sheetId="0">
-        <row r="6">
-          <cell r="C6">
-            <v>72</v>
-          </cell>
-          <cell r="D6">
-            <v>33</v>
-          </cell>
-          <cell r="E6">
-            <v>7</v>
-          </cell>
-          <cell r="F6">
-            <v>32</v>
-          </cell>
-          <cell r="G6">
-            <v>74</v>
-          </cell>
-          <cell r="H6">
-            <v>1194</v>
-          </cell>
-          <cell r="I6">
-            <v>3460</v>
-          </cell>
-          <cell r="J6">
-            <v>3480</v>
-          </cell>
-        </row>
-      </sheetData>
-      <sheetData sheetId="1"/>
-      <sheetData sheetId="2"/>
-      <sheetData sheetId="3"/>
-      <sheetData sheetId="4"/>
     </sheetDataSet>
   </externalBook>
 </externalLink>
@@ -1256,35 +1258,35 @@
         <v>33</v>
       </c>
       <c r="C6" s="4">
-        <f>'[8]B 2023-2027'!$C$6</f>
+        <f>'[4]B 2023-2027'!$C$6</f>
+        <v>73</v>
+      </c>
+      <c r="D6" s="4">
+        <f>'[4]B 2023-2027'!$D$6</f>
+        <v>34</v>
+      </c>
+      <c r="E6" s="4">
+        <f>'[4]B 2023-2027'!$E$6</f>
+        <v>7</v>
+      </c>
+      <c r="F6" s="4">
+        <f>'[4]B 2023-2027'!$F$6</f>
+        <v>32</v>
+      </c>
+      <c r="G6" s="4">
+        <f>'[4]B 2023-2027'!$G$6</f>
+        <v>75</v>
+      </c>
+      <c r="H6" s="4">
+        <f>'[4]B 2023-2027'!$H$6</f>
         <v>72</v>
       </c>
-      <c r="D6" s="4">
-        <f>'[8]B 2023-2027'!$D$6</f>
-        <v>33</v>
-      </c>
-      <c r="E6" s="4">
-        <f>'[8]B 2023-2027'!$E$6</f>
-        <v>7</v>
-      </c>
-      <c r="F6" s="4">
-        <f>'[8]B 2023-2027'!$F$6</f>
-        <v>32</v>
-      </c>
-      <c r="G6" s="4">
-        <f>'[8]B 2023-2027'!$G$6</f>
-        <v>74</v>
-      </c>
-      <c r="H6" s="4">
-        <f>'[8]B 2023-2027'!$H$6</f>
-        <v>1194</v>
-      </c>
       <c r="I6" s="4">
-        <f>'[8]B 2023-2027'!$I$6</f>
-        <v>3460</v>
+        <f>'[4]B 2023-2027'!$I$6</f>
+        <v>3461</v>
       </c>
       <c r="J6" s="4">
-        <f>'[8]B 2023-2027'!$J$6</f>
+        <f>'[4]B 2023-2027'!$J$6</f>
         <v>3480</v>
       </c>
       <c r="K6" s="4" t="s">
@@ -1299,35 +1301,35 @@
         <v>30</v>
       </c>
       <c r="C7" s="5">
-        <f>'[4]A 2025-2027'!$C$4</f>
+        <f>'[5]A 2025-2027'!$C$4</f>
         <v>19</v>
       </c>
       <c r="D7" s="5">
-        <f>'[4]A 2025-2027'!$D$4</f>
+        <f>'[5]A 2025-2027'!$D$4</f>
         <v>10</v>
       </c>
       <c r="E7" s="5">
-        <f>'[4]A 2025-2027'!$E$4</f>
+        <f>'[5]A 2025-2027'!$E$4</f>
         <v>0</v>
       </c>
       <c r="F7" s="5">
-        <f>'[4]A 2025-2027'!$F$4</f>
+        <f>'[5]A 2025-2027'!$F$4</f>
         <v>9</v>
       </c>
       <c r="G7" s="5">
-        <f>'[4]A 2025-2027'!$G$4</f>
+        <f>'[5]A 2025-2027'!$G$4</f>
         <v>23</v>
       </c>
       <c r="H7" s="5">
-        <f>'[4]A 2025-2027'!$H$4</f>
+        <f>'[5]A 2025-2027'!$H$4</f>
         <v>19</v>
       </c>
       <c r="I7" s="5">
-        <f>'[4]A 2025-2027'!$I$4</f>
+        <f>'[5]A 2025-2027'!$I$4</f>
         <v>973</v>
       </c>
       <c r="J7" s="5">
-        <f>'[4]A 2025-2027'!$J$4</f>
+        <f>'[5]A 2025-2027'!$J$4</f>
         <v>943</v>
       </c>
       <c r="K7" s="9">
@@ -1342,35 +1344,35 @@
         <v>30</v>
       </c>
       <c r="C8" s="4">
-        <f>'[5]M2 2025-2027'!$C$2</f>
+        <f>'[6]M2 2025-2027'!$C$2</f>
         <v>18</v>
       </c>
       <c r="D8" s="4">
-        <f>'[5]M2 2025-2027'!$D$2</f>
+        <f>'[6]M2 2025-2027'!$D$2</f>
         <v>5</v>
       </c>
       <c r="E8" s="4">
-        <f>'[5]M2 2025-2027'!$E$2</f>
+        <f>'[6]M2 2025-2027'!$E$2</f>
         <v>0</v>
       </c>
       <c r="F8" s="4">
-        <f>'[5]M2 2025-2027'!$F$2</f>
+        <f>'[6]M2 2025-2027'!$F$2</f>
         <v>13</v>
       </c>
       <c r="G8" s="4">
-        <f>'[5]M2 2025-2027'!$G$2</f>
+        <f>'[6]M2 2025-2027'!$G$2</f>
         <v>16</v>
       </c>
       <c r="H8" s="4">
-        <f>'[5]M2 2025-2027'!$H$2</f>
+        <f>'[6]M2 2025-2027'!$H$2</f>
         <v>38</v>
       </c>
       <c r="I8" s="4">
-        <f>'[5]M2 2025-2027'!$I$2</f>
+        <f>'[6]M2 2025-2027'!$I$2</f>
         <v>1414</v>
       </c>
       <c r="J8" s="4">
-        <f>'[5]M2 2025-2027'!$J$2</f>
+        <f>'[6]M2 2025-2027'!$J$2</f>
         <v>1595</v>
       </c>
       <c r="K8" s="4"/>
@@ -1382,11 +1384,11 @@
       <c r="B9" s="5"/>
       <c r="C9" s="7">
         <f>SUM(C2:C8)</f>
-        <v>478</v>
+        <v>479</v>
       </c>
       <c r="D9" s="7">
         <f t="shared" ref="D9:J9" si="0">SUM(D2:D8)</f>
-        <v>263</v>
+        <v>264</v>
       </c>
       <c r="E9" s="7">
         <f t="shared" si="0"/>
@@ -1398,15 +1400,15 @@
       </c>
       <c r="G9" s="7">
         <f t="shared" si="0"/>
-        <v>450</v>
+        <v>451</v>
       </c>
       <c r="H9" s="7">
         <f t="shared" si="0"/>
-        <v>1526</v>
+        <v>404</v>
       </c>
       <c r="I9" s="7">
         <f t="shared" si="0"/>
-        <v>20464</v>
+        <v>20465</v>
       </c>
       <c r="J9" s="7">
         <f t="shared" si="0"/>
@@ -1435,19 +1437,19 @@
         <v>27</v>
       </c>
       <c r="C11" s="5">
-        <f>[6]powercup!$C$12</f>
+        <f>[7]powercup!$C$12</f>
         <v>179</v>
       </c>
       <c r="D11" s="5">
-        <f>[6]powercup!$D$12</f>
+        <f>[7]powercup!$D$12</f>
         <v>109</v>
       </c>
       <c r="E11" s="5">
-        <f>[6]powercup!$E$12</f>
+        <f>[7]powercup!$E$12</f>
         <v>0</v>
       </c>
       <c r="F11" s="5">
-        <f>[6]powercup!$F$12</f>
+        <f>[7]powercup!$F$12</f>
         <v>70</v>
       </c>
       <c r="G11" s="5">
@@ -1459,11 +1461,11 @@
         <v>140</v>
       </c>
       <c r="I11" s="5">
-        <f>[6]powercup!$G$12</f>
+        <f>[7]powercup!$G$12</f>
         <v>8881</v>
       </c>
       <c r="J11" s="5">
-        <f>[6]powercup!$H$12</f>
+        <f>[7]powercup!$H$12</f>
         <v>8297</v>
       </c>
       <c r="K11" s="5"/>
@@ -1476,35 +1478,35 @@
         <v>32</v>
       </c>
       <c r="C12" s="4">
-        <f>[7]all!$C$8</f>
+        <f>[8]all!$C$8</f>
         <v>9</v>
       </c>
       <c r="D12" s="4">
-        <f>[7]all!$D$8</f>
+        <f>[8]all!$D$8</f>
         <v>0</v>
       </c>
       <c r="E12" s="4">
-        <f>[7]all!$E$8</f>
+        <f>[8]all!$E$8</f>
         <v>0</v>
       </c>
       <c r="F12" s="4">
-        <f>[7]all!$F$8</f>
+        <f>[8]all!$F$8</f>
         <v>9</v>
       </c>
       <c r="G12" s="4">
-        <f>[7]all!$G$8</f>
+        <f>[8]all!$G$8</f>
         <v>0</v>
       </c>
       <c r="H12" s="4">
-        <f>[7]all!$H$8</f>
+        <f>[8]all!$H$8</f>
         <v>27</v>
       </c>
       <c r="I12" s="4">
-        <f>[7]all!$I$8</f>
+        <f>[8]all!$I$8</f>
         <v>260</v>
       </c>
       <c r="J12" s="4">
-        <f>[7]all!$J$8</f>
+        <f>[8]all!$J$8</f>
         <v>391</v>
       </c>
       <c r="K12" s="4"/>
@@ -1527,11 +1529,11 @@
       <c r="B14" s="4"/>
       <c r="C14" s="4">
         <f>SUM(C9:C12)</f>
-        <v>666</v>
+        <v>667</v>
       </c>
       <c r="D14" s="4">
         <f t="shared" ref="D14:J14" si="1">SUM(D9:D12)</f>
-        <v>372</v>
+        <v>373</v>
       </c>
       <c r="E14" s="4">
         <f t="shared" si="1"/>
@@ -1543,15 +1545,15 @@
       </c>
       <c r="G14" s="4">
         <f t="shared" si="1"/>
-        <v>668</v>
+        <v>669</v>
       </c>
       <c r="H14" s="4">
         <f t="shared" si="1"/>
-        <v>1693</v>
+        <v>571</v>
       </c>
       <c r="I14" s="4">
         <f t="shared" si="1"/>
-        <v>29605</v>
+        <v>29606</v>
       </c>
       <c r="J14" s="4">
         <f t="shared" si="1"/>
